--- a/data/trans_dic/P02E$ssociales-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,99</t>
+          <t>0,0; 10,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,98</t>
+          <t>0,0; 16,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,24</t>
+          <t>0,0; 9,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,0; 5,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 6,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,86</t>
+          <t>0,0; 4,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,73</t>
+          <t>0,0; 5,77</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,17</t>
+          <t>0,24; 2,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,56</t>
+          <t>0,19; 1,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,49</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,22</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,34</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,13</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,29</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,98</t>
+          <t>0,1; 0,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,92</t>
+          <t>0,43; 3,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,27 +1028,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,33</t>
+          <t>0,5; 4,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,03</t>
+          <t>0,21; 2,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,34</t>
+          <t>0,27; 2,58</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 19,37</t>
+          <t>2,07; 18,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,53</t>
+          <t>0,0; 16,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 9,79</t>
+          <t>1,14; 10,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 17,33</t>
+          <t>1,96; 17,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 10,98</t>
+          <t>2,2; 10,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 13,68</t>
+          <t>3,05; 13,98</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,44</t>
+          <t>0,0; 40,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,71; 38,9</t>
+          <t>4,57; 39,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,67</t>
+          <t>0,0; 24,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,66</t>
+          <t>0,0; 9,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 15,92</t>
+          <t>2,01; 16,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,12</t>
+          <t>0,0; 14,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 12,23</t>
+          <t>1,44; 12,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,37; 18,51</t>
+          <t>4,26; 20,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,93</t>
+          <t>0,0; 11,3</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,87</t>
+          <t>0,0; 34,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,78</t>
+          <t>0,0; 47,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,12; 26,91</t>
+          <t>5,05; 26,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,94</t>
+          <t>0,0; 15,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 21,69</t>
+          <t>5,28; 23,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 17,29</t>
+          <t>1,5; 17,76</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,54</t>
+          <t>0,95; 2,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,46</t>
+          <t>0,67; 2,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,07</t>
+          <t>0,1; 1,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,96</t>
+          <t>0,81; 2,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,7</t>
+          <t>0,48; 1,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,84</t>
+          <t>0,18; 0,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,99</t>
+          <t>1,01; 2,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,66</t>
+          <t>0,73; 1,72</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1909</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4915</t>
+          <t>0; 4222</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6511</t>
+          <t>0; 6679</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4672</t>
+          <t>0; 4934</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4082</t>
+          <t>0; 5096</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1872</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4364</t>
+          <t>0; 5346</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6930</t>
+          <t>0; 6120</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 7479</t>
+          <t>0; 7542</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2000</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5490</t>
+          <t>0; 4436</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6906</t>
+          <t>0; 6677</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2026</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>927; 8468</t>
+          <t>934; 8500</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1871</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2022</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1015; 9454</t>
+          <t>1143; 9899</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6626</t>
+          <t>0; 5938</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1967</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5612</t>
+          <t>0; 6279</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5759</t>
+          <t>0; 5226</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5269</t>
+          <t>0; 5835</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6482</t>
+          <t>0; 7025</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5251</t>
+          <t>0; 5456</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7118</t>
+          <t>0; 5916</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>999; 9655</t>
+          <t>977; 9333</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6792</t>
+          <t>0; 6614</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2035</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>988; 8975</t>
+          <t>982; 9019</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2104</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6182</t>
+          <t>0; 6183</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6105</t>
+          <t>0; 6568</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>903; 7898</t>
+          <t>904; 7805</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7219</t>
+          <t>0; 7036</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1123; 9945</t>
+          <t>1021; 9918</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>208; 7939</t>
+          <t>913; 8737</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1891</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1034; 9517</t>
+          <t>1016; 8887</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6653</t>
+          <t>0; 6613</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1944</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1105; 9843</t>
+          <t>1148; 10053</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1115; 9842</t>
+          <t>1111; 10003</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1961</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3980; 16441</t>
+          <t>3291; 15345</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3066; 13269</t>
+          <t>2963; 13568</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5023</t>
+          <t>0; 5705</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1050; 8673</t>
+          <t>1019; 8778</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4817</t>
+          <t>0; 5106</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4532</t>
+          <t>0; 4453</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>944; 7528</t>
+          <t>948; 7881</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5146</t>
+          <t>0; 5266</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>874; 7473</t>
+          <t>881; 7394</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3039; 12875</t>
+          <t>2965; 14000</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6308</t>
+          <t>0; 6517</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1706</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5362</t>
+          <t>0; 5213</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 6199</t>
+          <t>0; 5935</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 2103</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2109; 11096</t>
+          <t>2083; 11129</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 8053</t>
+          <t>0; 6760</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 1988</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2951; 12185</t>
+          <t>2964; 13097</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>845; 9916</t>
+          <t>860; 10188</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 5789</t>
+          <t>0; 6502</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9290; 24976</t>
+          <t>9346; 26343</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5209; 18585</t>
+          <t>5085; 18973</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1878; 10719</t>
+          <t>1050; 10784</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12289; 29755</t>
+          <t>12338; 30853</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5172; 18929</t>
+          <t>5318; 19067</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2909; 13638</t>
+          <t>2875; 13372</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>25836; 49672</t>
+          <t>25363; 50094</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>12635; 31076</t>
+          <t>13685; 32176</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$ssociales-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Edad-trans_dic.xlsx
@@ -683,22 +683,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,3</t>
+          <t>0,0; 12,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,39</t>
+          <t>0,0; 17,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,76</t>
+          <t>0,0; 8,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,01</t>
+          <t>0,0; 4,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,63</t>
+          <t>0,0; 6,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,77</t>
+          <t>0,0; 6,53</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,18</t>
+          <t>0,24; 2,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,64</t>
+          <t>0,3; 1,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
     </row>
@@ -903,17 +903,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,94</t>
+          <t>0,09; 0,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,94</t>
+          <t>0,42; 3,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,12</t>
+          <t>0,0; 5,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,28</t>
+          <t>0,5; 4,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,02</t>
+          <t>0,23; 2,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,58</t>
+          <t>0,27; 2,55</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 18,08</t>
+          <t>2,23; 19,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,43</t>
+          <t>0,0; 17,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 10,0</t>
+          <t>1,08; 9,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 17,62</t>
+          <t>1,88; 16,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 10,25</t>
+          <t>2,65; 10,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 13,98</t>
+          <t>2,54; 13,18</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,25</t>
+          <t>0,0; 44,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,57; 39,38</t>
+          <t>4,55; 38,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,03</t>
+          <t>0,0; 23,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,49</t>
+          <t>0,0; 9,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,01; 16,67</t>
+          <t>2,0; 16,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,45</t>
+          <t>0,0; 11,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,1</t>
+          <t>1,45; 11,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,26; 20,12</t>
+          <t>4,41; 18,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,3</t>
+          <t>0,0; 10,23</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,87</t>
+          <t>0,0; 30,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,66</t>
+          <t>0,0; 47,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,12 +1358,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,05; 26,99</t>
+          <t>5,03; 26,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,06</t>
+          <t>0,0; 13,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 23,31</t>
+          <t>4,0; 23,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 17,76</t>
+          <t>1,5; 16,12</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,67</t>
+          <t>1,0; 2,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,51</t>
+          <t>0,66; 2,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,07</t>
+          <t>0,19; 1,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,03</t>
+          <t>0,79; 1,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,72</t>
+          <t>0,45; 1,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,82</t>
+          <t>0,17; 0,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,0</t>
+          <t>1,02; 1,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,72</t>
+          <t>0,7; 1,75</t>
         </is>
       </c>
     </row>
@@ -1755,22 +1755,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4222</t>
+          <t>0; 5163</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6679</t>
+          <t>0; 7301</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4934</t>
+          <t>0; 4354</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5096</t>
+          <t>0; 5054</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5346</t>
+          <t>0; 5261</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6120</t>
+          <t>0; 6059</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 7542</t>
+          <t>0; 8528</t>
         </is>
       </c>
     </row>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4436</t>
+          <t>0; 5441</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6677</t>
+          <t>0; 6173</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>934; 8500</t>
+          <t>921; 8167</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1143; 9899</t>
+          <t>1843; 11299</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5938</t>
+          <t>0; 6011</t>
         </is>
       </c>
     </row>
@@ -2081,42 +2081,42 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6279</t>
+          <t>0; 6413</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5226</t>
+          <t>0; 5704</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5835</t>
+          <t>0; 5230</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7025</t>
+          <t>0; 6982</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5456</t>
+          <t>0; 4015</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5916</t>
+          <t>0; 6397</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>977; 9333</t>
+          <t>924; 9604</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6614</t>
+          <t>0; 7198</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>982; 9019</t>
+          <t>963; 8958</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2254,32 +2254,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6183</t>
+          <t>0; 6095</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6568</t>
+          <t>0; 5201</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>904; 7805</t>
+          <t>910; 7857</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7036</t>
+          <t>0; 6141</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1021; 9918</t>
+          <t>1121; 10452</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>913; 8737</t>
+          <t>909; 8662</t>
         </is>
       </c>
     </row>
@@ -2407,12 +2407,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1016; 8887</t>
+          <t>1094; 9550</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6613</t>
+          <t>0; 6925</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2422,12 +2422,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1148; 10053</t>
+          <t>1089; 10029</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1111; 10003</t>
+          <t>1069; 9465</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3291; 15345</t>
+          <t>3960; 15796</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2963; 13568</t>
+          <t>2463; 12784</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5705</t>
+          <t>0; 6246</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1019; 8778</t>
+          <t>1014; 8559</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5106</t>
+          <t>0; 4908</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4453</t>
+          <t>0; 4502</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>948; 7881</t>
+          <t>946; 7971</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5266</t>
+          <t>0; 4243</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>881; 7394</t>
+          <t>887; 6977</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2965; 14000</t>
+          <t>3068; 13162</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6517</t>
+          <t>0; 5903</t>
         </is>
       </c>
     </row>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5213</t>
+          <t>0; 4525</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5935</t>
+          <t>0; 5914</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2083; 11129</t>
+          <t>2075; 10862</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 6760</t>
+          <t>0; 5837</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2964; 13097</t>
+          <t>2247; 13148</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>860; 10188</t>
+          <t>860; 9245</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6502</t>
+          <t>0; 6168</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9346; 26343</t>
+          <t>9871; 25870</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5085; 18973</t>
+          <t>5009; 19007</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1050; 10784</t>
+          <t>1897; 11091</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12338; 30853</t>
+          <t>12014; 29190</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5318; 19067</t>
+          <t>5034; 18590</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2875; 13372</t>
+          <t>2810; 13528</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>25363; 50094</t>
+          <t>25513; 49172</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13685; 32176</t>
+          <t>12998; 32692</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$ssociales-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
